--- a/src/scraping/data/test_data/tesco_argos.xlsx
+++ b/src/scraping/data/test_data/tesco_argos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\programming\competitor_product_search\src\scraping\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\programming\competitor_product_search\src\scraping\data\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB156789-9DC0-483D-B976-1DFAA94DB569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2A84B1-3537-4B44-96BF-095B84DF77DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10974" yWindow="1236" windowWidth="14070" windowHeight="8472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61260" yWindow="7575" windowWidth="16425" windowHeight="14010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
     <t>url</t>
   </si>
@@ -33,9 +33,6 @@
     <t>host</t>
   </si>
   <si>
-    <t>https://www.tesco.com/groceries/en-GB/products/276797313</t>
-  </si>
-  <si>
     <t>https://www.tesco.com/shop/en-GB/products/326405420</t>
   </si>
   <si>
@@ -46,36 +43,12 @@
   </si>
   <si>
     <t>tesco.com</t>
-  </si>
-  <si>
-    <t>error</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>discount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.tesco.com/shop/en-GB/products/325502056</t>
-  </si>
-  <si>
-    <t>tesco.com</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.tesco.com/shop/en-GB/products/325473961</t>
-  </si>
-  <si>
-    <t>https://www.tesco.com/shop/en-GB/products/317057148</t>
   </si>
   <si>
     <t>normal</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://www.tesco.com/shop/en-GB/products/312340157</t>
-  </si>
-  <si>
     <t>https://www.argos.co.uk/product/8189978</t>
   </si>
   <si>
@@ -86,13 +59,6 @@
   </si>
   <si>
     <t>https://www.argos.co.uk/product/4490582</t>
-  </si>
-  <si>
-    <t>https://www.argos.co.uk/product/8747437</t>
-  </si>
-  <si>
-    <t>https://www.argos.co.uk/product/7726844</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>https://www.argos.co.uk/product/3284476</t>
@@ -105,11 +71,47 @@
     <t>error</t>
   </si>
   <si>
+    <t>https://www.argos.co.uk/browse/garden-and-diy/plant-and-lawn-care/grass-seed-and-feed/c:1040915</t>
+  </si>
+  <si>
+    <t>membership</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tesco.com/groceries/en-GB/products/276797313</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tesco.com/groceries/en-GB/products/312841117</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/325602141</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/297568023</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/303350818</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/325296757</t>
+  </si>
+  <si>
+    <t>unavailable</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/320797857</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/8747437</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/7726844</t>
+  </si>
+  <si>
     <t>https://www.argos.co.uk/product/7123351</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.argos.co.uk/browse/garden-and-diy/plant-and-lawn-care/grass-seed-and-feed/c:1040915</t>
   </si>
 </sst>
 </file>
@@ -454,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -463,7 +465,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -474,171 +476,199 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{020150A2-A429-47E6-8DDF-195404F838CD}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{088A3374-DC49-4FF4-8803-48AE6DB6B735}"/>
-    <hyperlink ref="B13" r:id="rId3" xr:uid="{6DC4D07B-5C61-4CE0-9ADE-810460B7A53D}"/>
-    <hyperlink ref="B14" r:id="rId4" xr:uid="{47ACD45B-EC9D-42A3-9D17-6BAD18E978D3}"/>
-    <hyperlink ref="B8" r:id="rId5" xr:uid="{A1275989-991A-4972-A724-4D7FC3DDBFEB}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{B385037C-1203-4976-A792-3A560849F67A}"/>
-    <hyperlink ref="B11" r:id="rId7" xr:uid="{543370C0-136C-4722-B592-8891DDE3B3C3}"/>
-    <hyperlink ref="B12" r:id="rId8" xr:uid="{36D25C71-FD56-4E2A-A00E-460D8DECE662}"/>
-    <hyperlink ref="B9" r:id="rId9" xr:uid="{8199276D-7836-441C-BC9C-F8582E79E7C7}"/>
-    <hyperlink ref="B15" r:id="rId10" xr:uid="{DB27B9C8-0964-4936-9C1D-E68EDBE0A47F}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{D2FAE411-0B25-4EBB-90EF-A00C27AE3E8E}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{1ABAB2A1-A8D1-4608-92C1-263E5B0A9D87}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{6DB25518-2DFA-4C21-B25B-5A4E31024F42}"/>
+    <hyperlink ref="B7" r:id="rId4" xr:uid="{304E5075-3A28-4761-B314-E19CD7A96EB2}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{D41D06CC-637E-415C-AE16-81DBC84CC5CD}"/>
+    <hyperlink ref="B15" r:id="rId6" xr:uid="{231E1E47-7EF8-44EB-8E34-F814080B11B0}"/>
+    <hyperlink ref="B16" r:id="rId7" xr:uid="{540EACB5-8159-46DA-86DA-0357FC73847C}"/>
+    <hyperlink ref="B2" r:id="rId8" xr:uid="{F84D7906-6A25-400A-9B11-008048461435}"/>
+    <hyperlink ref="B3" r:id="rId9" xr:uid="{56793695-1B6D-4007-9634-96D58805B99B}"/>
+    <hyperlink ref="B9" r:id="rId10" xr:uid="{9080676F-8F3A-4161-801C-68E5778E139F}"/>
+    <hyperlink ref="B10" r:id="rId11" xr:uid="{EF9692D1-188C-487B-BDDA-5D22DCAE1C20}"/>
+    <hyperlink ref="B12" r:id="rId12" xr:uid="{156C918C-7C5D-43FE-A91C-F63A008D27F7}"/>
+    <hyperlink ref="B13" r:id="rId13" xr:uid="{9093B93A-724D-4E55-AA9C-3298BE74FF59}"/>
+    <hyperlink ref="B14" r:id="rId14" xr:uid="{A1BC2ADC-B33D-45C8-AEB3-4B989ECDA995}"/>
+    <hyperlink ref="B11" r:id="rId15" xr:uid="{B611121E-735B-4200-9B3A-35752B2D39D2}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{A51DA228-66DC-4FFC-8DA6-6468599D88B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/scraping/data/test_data/tesco_argos.xlsx
+++ b/src/scraping/data/test_data/tesco_argos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\programming\competitor_product_search\src\scraping\data\test_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kumo/programming/competitor_product_search/src/scraping/data/test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2A84B1-3537-4B44-96BF-095B84DF77DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1003168D-8CAF-8E4A-B3A6-689E0E80DDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61260" yWindow="7575" windowWidth="16425" windowHeight="14010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
   <si>
     <t>url</t>
   </si>
@@ -58,9 +58,6 @@
     <t>discount</t>
   </si>
   <si>
-    <t>https://www.argos.co.uk/product/4490582</t>
-  </si>
-  <si>
     <t>https://www.argos.co.uk/product/3284476</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -101,9 +98,6 @@
     <t>unavailable</t>
   </si>
   <si>
-    <t>https://www.tesco.com/shop/en-GB/products/320797857</t>
-  </si>
-  <si>
     <t>https://www.argos.co.uk/product/8747437</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -112,13 +106,24 @@
   </si>
   <si>
     <t>https://www.argos.co.uk/product/7123351</t>
+  </si>
+  <si>
+    <t>discount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/299425748</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/4667243</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,13 +462,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.19921875" customWidth="1"/>
-    <col min="3" max="3" width="11.09765625" customWidth="1"/>
+    <col min="1" max="1" width="30.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -474,31 +480,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
@@ -507,62 +513,62 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -573,78 +579,78 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A16" t="s">
+      <c r="B16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -667,8 +673,7 @@
     <hyperlink ref="B12" r:id="rId12" xr:uid="{156C918C-7C5D-43FE-A91C-F63A008D27F7}"/>
     <hyperlink ref="B13" r:id="rId13" xr:uid="{9093B93A-724D-4E55-AA9C-3298BE74FF59}"/>
     <hyperlink ref="B14" r:id="rId14" xr:uid="{A1BC2ADC-B33D-45C8-AEB3-4B989ECDA995}"/>
-    <hyperlink ref="B11" r:id="rId15" xr:uid="{B611121E-735B-4200-9B3A-35752B2D39D2}"/>
-    <hyperlink ref="B17" r:id="rId16" xr:uid="{A51DA228-66DC-4FFC-8DA6-6468599D88B5}"/>
+    <hyperlink ref="B17" r:id="rId15" xr:uid="{A51DA228-66DC-4FFC-8DA6-6468599D88B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
